--- a/data/m5/result/m5_treasury_signals.xlsx
+++ b/data/m5/result/m5_treasury_signals.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T174"/>
+  <dimension ref="A1:Y174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,6 +535,31 @@
       <c r="T1" s="1" t="inlineStr">
         <is>
           <t>flag_budget_drain</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>m5_score</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>m5_flag</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>m5_signal</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>source_quality</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>m5_comment</t>
         </is>
       </c>
     </row>
@@ -569,6 +594,25 @@
       <c r="T2" t="n">
         <v>0</v>
       </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -603,6 +647,25 @@
       <c r="T3" t="n">
         <v>0</v>
       </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -637,6 +700,25 @@
       <c r="T4" t="n">
         <v>0</v>
       </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -671,6 +753,25 @@
       <c r="T5" t="n">
         <v>0</v>
       </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -705,6 +806,25 @@
       <c r="T6" t="n">
         <v>0</v>
       </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -739,6 +859,25 @@
       <c r="T7" t="n">
         <v>0</v>
       </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -773,6 +912,25 @@
       <c r="T8" t="n">
         <v>0</v>
       </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -807,6 +965,25 @@
       <c r="T9" t="n">
         <v>0</v>
       </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -841,6 +1018,25 @@
       <c r="T10" t="n">
         <v>0</v>
       </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -875,6 +1071,25 @@
       <c r="T11" t="n">
         <v>0</v>
       </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -909,6 +1124,25 @@
       <c r="T12" t="n">
         <v>0</v>
       </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -943,6 +1177,25 @@
       <c r="T13" t="n">
         <v>0</v>
       </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -979,6 +1232,25 @@
       <c r="T14" t="n">
         <v>0</v>
       </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1015,6 +1287,25 @@
       <c r="T15" t="n">
         <v>0</v>
       </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1051,6 +1342,25 @@
       <c r="T16" t="n">
         <v>0</v>
       </c>
+      <c r="U16" t="n">
+        <v>31.31180228638708</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>31.31180228638708</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1087,6 +1397,25 @@
       <c r="T17" t="n">
         <v>0</v>
       </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1123,6 +1452,25 @@
       <c r="T18" t="n">
         <v>0</v>
       </c>
+      <c r="U18" t="n">
+        <v>1.514382119206986</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.514382119206986</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1159,6 +1507,25 @@
       <c r="T19" t="n">
         <v>0</v>
       </c>
+      <c r="U19" t="n">
+        <v>3.349354798770773</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.349354798770773</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1195,6 +1562,25 @@
       <c r="T20" t="n">
         <v>0</v>
       </c>
+      <c r="U20" t="n">
+        <v>4.94332878864985</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>4.94332878864985</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1231,6 +1617,25 @@
       <c r="T21" t="n">
         <v>0</v>
       </c>
+      <c r="U21" t="n">
+        <v>7.447838305524357</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>7.447838305524357</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1267,6 +1672,25 @@
       <c r="T22" t="n">
         <v>0</v>
       </c>
+      <c r="U22" t="n">
+        <v>21.51540144153193</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21.51540144153193</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1303,6 +1727,25 @@
       <c r="T23" t="n">
         <v>0</v>
       </c>
+      <c r="U23" t="n">
+        <v>24.3386333273401</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>24.3386333273401</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1339,6 +1782,25 @@
       <c r="T24" t="n">
         <v>0</v>
       </c>
+      <c r="U24" t="n">
+        <v>7.403866719463327</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>7.403866719463327</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1375,6 +1837,25 @@
       <c r="T25" t="n">
         <v>1</v>
       </c>
+      <c r="U25" t="n">
+        <v>62.84347842759421</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
+        <v>62.84347842759421</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1417,6 +1898,25 @@
       <c r="T26" t="n">
         <v>0</v>
       </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1459,6 +1959,25 @@
       <c r="T27" t="n">
         <v>0</v>
       </c>
+      <c r="U27" t="n">
+        <v>12.32317710399879</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>12.32317710399879</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1501,6 +2020,25 @@
       <c r="T28" t="n">
         <v>0</v>
       </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -1543,6 +2081,25 @@
       <c r="T29" t="n">
         <v>0</v>
       </c>
+      <c r="U29" t="n">
+        <v>3.738801570296642</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>3.738801570296642</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1585,6 +2142,25 @@
       <c r="T30" t="n">
         <v>0</v>
       </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -1627,6 +2203,25 @@
       <c r="T31" t="n">
         <v>0</v>
       </c>
+      <c r="U31" t="n">
+        <v>11.80358829084042</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>11.80358829084042</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -1669,6 +2264,25 @@
       <c r="T32" t="n">
         <v>0</v>
       </c>
+      <c r="U32" t="n">
+        <v>1.180639265964296</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.180639265964296</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -1711,6 +2325,25 @@
       <c r="T33" t="n">
         <v>0</v>
       </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -1753,6 +2386,25 @@
       <c r="T34" t="n">
         <v>0</v>
       </c>
+      <c r="U34" t="n">
+        <v>25.71342307933995</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>25.71342307933995</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -1795,6 +2447,25 @@
       <c r="T35" t="n">
         <v>0</v>
       </c>
+      <c r="U35" t="n">
+        <v>19.67808910082016</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>19.67808910082016</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -1837,6 +2508,25 @@
       <c r="T36" t="n">
         <v>0</v>
       </c>
+      <c r="U36" t="n">
+        <v>7.18772008858159</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>7.18772008858159</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -1879,6 +2569,25 @@
       <c r="T37" t="n">
         <v>1</v>
       </c>
+      <c r="U37" t="n">
+        <v>71.84877325513982</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="n">
+        <v>71.84877325513982</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -1921,6 +2630,25 @@
       <c r="T38" t="n">
         <v>0</v>
       </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -1963,6 +2691,25 @@
       <c r="T39" t="n">
         <v>0</v>
       </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -2005,6 +2752,25 @@
       <c r="T40" t="n">
         <v>0</v>
       </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -2047,6 +2813,25 @@
       <c r="T41" t="n">
         <v>0</v>
       </c>
+      <c r="U41" t="n">
+        <v>18.01019540591681</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>18.01019540591681</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -2089,6 +2874,25 @@
       <c r="T42" t="n">
         <v>0</v>
       </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -2131,6 +2935,25 @@
       <c r="T43" t="n">
         <v>0</v>
       </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -2173,6 +2996,25 @@
       <c r="T44" t="n">
         <v>0</v>
       </c>
+      <c r="U44" t="n">
+        <v>19.11912682959979</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>19.11912682959979</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -2215,6 +3057,25 @@
       <c r="T45" t="n">
         <v>0</v>
       </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -2257,6 +3118,25 @@
       <c r="T46" t="n">
         <v>0</v>
       </c>
+      <c r="U46" t="n">
+        <v>17.47795298942362</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>17.47795298942362</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -2299,6 +3179,25 @@
       <c r="T47" t="n">
         <v>0</v>
       </c>
+      <c r="U47" t="n">
+        <v>1.647238993519453</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.647238993519453</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -2341,6 +3240,25 @@
       <c r="T48" t="n">
         <v>0</v>
       </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -2383,6 +3301,25 @@
       <c r="T49" t="n">
         <v>1</v>
       </c>
+      <c r="U49" t="n">
+        <v>67.99755909721688</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" t="n">
+        <v>67.99755909721688</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -2425,6 +3362,25 @@
       <c r="T50" t="n">
         <v>0</v>
       </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -2467,6 +3423,25 @@
       <c r="T51" t="n">
         <v>0</v>
       </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -2509,6 +3484,25 @@
       <c r="T52" t="n">
         <v>0</v>
       </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -2551,6 +3545,25 @@
       <c r="T53" t="n">
         <v>0</v>
       </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -2593,6 +3606,25 @@
       <c r="T54" t="n">
         <v>0</v>
       </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -2635,6 +3667,25 @@
       <c r="T55" t="n">
         <v>0</v>
       </c>
+      <c r="U55" t="n">
+        <v>10.49995068849069</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>10.49995068849069</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -2677,6 +3728,25 @@
       <c r="T56" t="n">
         <v>0</v>
       </c>
+      <c r="U56" t="n">
+        <v>3.944920744501775</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>3.944920744501775</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -2719,6 +3789,25 @@
       <c r="T57" t="n">
         <v>0</v>
       </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -2761,6 +3850,25 @@
       <c r="T58" t="n">
         <v>0</v>
       </c>
+      <c r="U58" t="n">
+        <v>12.07512849378524</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" t="n">
+        <v>12.07512849378524</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -2803,6 +3911,25 @@
       <c r="T59" t="n">
         <v>0</v>
       </c>
+      <c r="U59" t="n">
+        <v>6.488128742929387</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
+        <v>6.488128742929387</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -2845,6 +3972,25 @@
       <c r="T60" t="n">
         <v>0</v>
       </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -2887,6 +4033,25 @@
       <c r="T61" t="n">
         <v>0</v>
       </c>
+      <c r="U61" t="n">
+        <v>39.66649672575383</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>39.66649672575383</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -2929,6 +4094,25 @@
       <c r="T62" t="n">
         <v>0</v>
       </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -2971,6 +4155,25 @@
       <c r="T63" t="n">
         <v>0</v>
       </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -3013,6 +4216,25 @@
       <c r="T64" t="n">
         <v>0</v>
       </c>
+      <c r="U64" t="n">
+        <v>9.011440196405834</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
+        <v>9.011440196405834</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -3055,6 +4277,25 @@
       <c r="T65" t="n">
         <v>0</v>
       </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -3097,6 +4338,25 @@
       <c r="T66" t="n">
         <v>0</v>
       </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -3139,6 +4399,25 @@
       <c r="T67" t="n">
         <v>0</v>
       </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -3181,6 +4460,25 @@
       <c r="T68" t="n">
         <v>0</v>
       </c>
+      <c r="U68" t="n">
+        <v>8.149895071688599</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" t="n">
+        <v>8.149895071688599</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -3223,6 +4521,25 @@
       <c r="T69" t="n">
         <v>0</v>
       </c>
+      <c r="U69" t="n">
+        <v>3.60913069426644</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
+        <v>3.60913069426644</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -3265,6 +4582,25 @@
       <c r="T70" t="n">
         <v>0</v>
       </c>
+      <c r="U70" t="n">
+        <v>0.1884001717870954</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0.1884001717870954</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -3307,6 +4643,25 @@
       <c r="T71" t="n">
         <v>0</v>
       </c>
+      <c r="U71" t="n">
+        <v>14.33824051920254</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
+        <v>14.33824051920254</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -3349,6 +4704,25 @@
       <c r="T72" t="n">
         <v>0</v>
       </c>
+      <c r="U72" t="n">
+        <v>3.284512667559727</v>
+      </c>
+      <c r="V72" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" t="n">
+        <v>3.284512667559727</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -3391,6 +4765,25 @@
       <c r="T73" t="n">
         <v>0</v>
       </c>
+      <c r="U73" t="n">
+        <v>40.11236916897781</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" t="n">
+        <v>40.11236916897781</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -3433,6 +4826,25 @@
       <c r="T74" t="n">
         <v>0</v>
       </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -3475,6 +4887,25 @@
       <c r="T75" t="n">
         <v>0</v>
       </c>
+      <c r="U75" t="n">
+        <v>3.832532555872352</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" t="n">
+        <v>3.832532555872352</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -3517,6 +4948,25 @@
       <c r="T76" t="n">
         <v>0</v>
       </c>
+      <c r="U76" t="n">
+        <v>0.524656679862378</v>
+      </c>
+      <c r="V76" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" t="n">
+        <v>0.524656679862378</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -3559,6 +5009,25 @@
       <c r="T77" t="n">
         <v>0</v>
       </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -3601,6 +5070,25 @@
       <c r="T78" t="n">
         <v>0</v>
       </c>
+      <c r="U78" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -3643,6 +5131,25 @@
       <c r="T79" t="n">
         <v>0</v>
       </c>
+      <c r="U79" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -3685,6 +5192,25 @@
       <c r="T80" t="n">
         <v>0</v>
       </c>
+      <c r="U80" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -3727,6 +5253,25 @@
       <c r="T81" t="n">
         <v>0</v>
       </c>
+      <c r="U81" t="n">
+        <v>15.18012826002961</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" t="n">
+        <v>15.18012826002961</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -3769,6 +5314,25 @@
       <c r="T82" t="n">
         <v>0</v>
       </c>
+      <c r="U82" t="n">
+        <v>19.01568152878179</v>
+      </c>
+      <c r="V82" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" t="n">
+        <v>19.01568152878179</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -3811,6 +5375,25 @@
       <c r="T83" t="n">
         <v>0</v>
       </c>
+      <c r="U83" t="n">
+        <v>7.100404541905269</v>
+      </c>
+      <c r="V83" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" t="n">
+        <v>7.100404541905269</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -3853,6 +5436,25 @@
       <c r="T84" t="n">
         <v>0</v>
       </c>
+      <c r="U84" t="n">
+        <v>7.558557639910604</v>
+      </c>
+      <c r="V84" t="n">
+        <v>0</v>
+      </c>
+      <c r="W84" t="n">
+        <v>7.558557639910604</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -3895,6 +5497,25 @@
       <c r="T85" t="n">
         <v>1</v>
       </c>
+      <c r="U85" t="n">
+        <v>69.60444737504741</v>
+      </c>
+      <c r="V85" t="n">
+        <v>1</v>
+      </c>
+      <c r="W85" t="n">
+        <v>69.60444737504741</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -3937,6 +5558,25 @@
       <c r="T86" t="n">
         <v>0</v>
       </c>
+      <c r="U86" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" t="n">
+        <v>0</v>
+      </c>
+      <c r="W86" t="n">
+        <v>0</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -3979,6 +5619,25 @@
       <c r="T87" t="n">
         <v>0</v>
       </c>
+      <c r="U87" t="n">
+        <v>14.8567584753323</v>
+      </c>
+      <c r="V87" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" t="n">
+        <v>14.8567584753323</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -4021,6 +5680,25 @@
       <c r="T88" t="n">
         <v>0</v>
       </c>
+      <c r="U88" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" t="n">
+        <v>0</v>
+      </c>
+      <c r="W88" t="n">
+        <v>0</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -4063,6 +5741,25 @@
       <c r="T89" t="n">
         <v>0</v>
       </c>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" t="n">
+        <v>0</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -4105,6 +5802,25 @@
       <c r="T90" t="n">
         <v>0</v>
       </c>
+      <c r="U90" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" t="n">
+        <v>0</v>
+      </c>
+      <c r="W90" t="n">
+        <v>0</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -4147,6 +5863,25 @@
       <c r="T91" t="n">
         <v>0</v>
       </c>
+      <c r="U91" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" t="n">
+        <v>0</v>
+      </c>
+      <c r="W91" t="n">
+        <v>0</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -4189,6 +5924,25 @@
       <c r="T92" t="n">
         <v>0</v>
       </c>
+      <c r="U92" t="n">
+        <v>3.945362385759966</v>
+      </c>
+      <c r="V92" t="n">
+        <v>0</v>
+      </c>
+      <c r="W92" t="n">
+        <v>3.945362385759966</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -4231,6 +5985,25 @@
       <c r="T93" t="n">
         <v>0</v>
       </c>
+      <c r="U93" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" t="n">
+        <v>0</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -4273,6 +6046,25 @@
       <c r="T94" t="n">
         <v>0</v>
       </c>
+      <c r="U94" t="n">
+        <v>0</v>
+      </c>
+      <c r="V94" t="n">
+        <v>0</v>
+      </c>
+      <c r="W94" t="n">
+        <v>0</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
@@ -4315,6 +6107,25 @@
       <c r="T95" t="n">
         <v>0</v>
       </c>
+      <c r="U95" t="n">
+        <v>13.96411074877762</v>
+      </c>
+      <c r="V95" t="n">
+        <v>0</v>
+      </c>
+      <c r="W95" t="n">
+        <v>13.96411074877762</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -4357,6 +6168,25 @@
       <c r="T96" t="n">
         <v>0</v>
       </c>
+      <c r="U96" t="n">
+        <v>10.45971596391353</v>
+      </c>
+      <c r="V96" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" t="n">
+        <v>10.45971596391353</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -4399,6 +6229,25 @@
       <c r="T97" t="n">
         <v>0</v>
       </c>
+      <c r="U97" t="n">
+        <v>40.55866289905549</v>
+      </c>
+      <c r="V97" t="n">
+        <v>0</v>
+      </c>
+      <c r="W97" t="n">
+        <v>40.55866289905549</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -4441,6 +6290,25 @@
       <c r="T98" t="n">
         <v>0</v>
       </c>
+      <c r="U98" t="n">
+        <v>0</v>
+      </c>
+      <c r="V98" t="n">
+        <v>0</v>
+      </c>
+      <c r="W98" t="n">
+        <v>0</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -4483,6 +6351,25 @@
       <c r="T99" t="n">
         <v>0</v>
       </c>
+      <c r="U99" t="n">
+        <v>0</v>
+      </c>
+      <c r="V99" t="n">
+        <v>0</v>
+      </c>
+      <c r="W99" t="n">
+        <v>0</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -4525,6 +6412,25 @@
       <c r="T100" t="n">
         <v>0</v>
       </c>
+      <c r="U100" t="n">
+        <v>0</v>
+      </c>
+      <c r="V100" t="n">
+        <v>0</v>
+      </c>
+      <c r="W100" t="n">
+        <v>0</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -4567,6 +6473,25 @@
       <c r="T101" t="n">
         <v>0</v>
       </c>
+      <c r="U101" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" t="n">
+        <v>0</v>
+      </c>
+      <c r="W101" t="n">
+        <v>0</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -4609,6 +6534,25 @@
       <c r="T102" t="n">
         <v>0</v>
       </c>
+      <c r="U102" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" t="n">
+        <v>0</v>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -4651,6 +6595,25 @@
       <c r="T103" t="n">
         <v>0</v>
       </c>
+      <c r="U103" t="n">
+        <v>5.977741426187179</v>
+      </c>
+      <c r="V103" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" t="n">
+        <v>5.977741426187179</v>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -4693,6 +6656,25 @@
       <c r="T104" t="n">
         <v>0</v>
       </c>
+      <c r="U104" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" t="n">
+        <v>0</v>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -4735,6 +6717,25 @@
       <c r="T105" t="n">
         <v>0</v>
       </c>
+      <c r="U105" t="n">
+        <v>26.28245547984875</v>
+      </c>
+      <c r="V105" t="n">
+        <v>0</v>
+      </c>
+      <c r="W105" t="n">
+        <v>26.28245547984875</v>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -4777,6 +6778,25 @@
       <c r="T106" t="n">
         <v>0</v>
       </c>
+      <c r="U106" t="n">
+        <v>10.72810571312376</v>
+      </c>
+      <c r="V106" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" t="n">
+        <v>10.72810571312376</v>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -4819,6 +6839,25 @@
       <c r="T107" t="n">
         <v>0</v>
       </c>
+      <c r="U107" t="n">
+        <v>14.55976289683969</v>
+      </c>
+      <c r="V107" t="n">
+        <v>0</v>
+      </c>
+      <c r="W107" t="n">
+        <v>14.55976289683969</v>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -4861,6 +6900,25 @@
       <c r="T108" t="n">
         <v>0</v>
       </c>
+      <c r="U108" t="n">
+        <v>5.985294345553484</v>
+      </c>
+      <c r="V108" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" t="n">
+        <v>5.985294345553484</v>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -4903,6 +6961,25 @@
       <c r="T109" t="n">
         <v>0</v>
       </c>
+      <c r="U109" t="n">
+        <v>35.88504600927825</v>
+      </c>
+      <c r="V109" t="n">
+        <v>0</v>
+      </c>
+      <c r="W109" t="n">
+        <v>35.88504600927825</v>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -4957,6 +7034,25 @@
       <c r="T110" t="n">
         <v>0</v>
       </c>
+      <c r="U110" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" t="n">
+        <v>0</v>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
@@ -5013,6 +7109,25 @@
       <c r="T111" t="n">
         <v>0</v>
       </c>
+      <c r="U111" t="n">
+        <v>6.696048049087956</v>
+      </c>
+      <c r="V111" t="n">
+        <v>0</v>
+      </c>
+      <c r="W111" t="n">
+        <v>6.696048049087956</v>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -5069,6 +7184,25 @@
       <c r="T112" t="n">
         <v>0</v>
       </c>
+      <c r="U112" t="n">
+        <v>7.68713408145351</v>
+      </c>
+      <c r="V112" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" t="n">
+        <v>7.68713408145351</v>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -5125,6 +7259,25 @@
       <c r="T113" t="n">
         <v>0</v>
       </c>
+      <c r="U113" t="n">
+        <v>0</v>
+      </c>
+      <c r="V113" t="n">
+        <v>0</v>
+      </c>
+      <c r="W113" t="n">
+        <v>0</v>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -5181,6 +7334,25 @@
       <c r="T114" t="n">
         <v>0</v>
       </c>
+      <c r="U114" t="n">
+        <v>0</v>
+      </c>
+      <c r="V114" t="n">
+        <v>0</v>
+      </c>
+      <c r="W114" t="n">
+        <v>0</v>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
@@ -5241,6 +7413,25 @@
       <c r="T115" t="n">
         <v>0</v>
       </c>
+      <c r="U115" t="n">
+        <v>0</v>
+      </c>
+      <c r="V115" t="n">
+        <v>0</v>
+      </c>
+      <c r="W115" t="n">
+        <v>0</v>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -5301,6 +7492,25 @@
       <c r="T116" t="n">
         <v>1</v>
       </c>
+      <c r="U116" t="n">
+        <v>25.11736139214893</v>
+      </c>
+      <c r="V116" t="n">
+        <v>1</v>
+      </c>
+      <c r="W116" t="n">
+        <v>25.11736139214893</v>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -5361,6 +7571,25 @@
       <c r="T117" t="n">
         <v>1</v>
       </c>
+      <c r="U117" t="n">
+        <v>24.67100721308353</v>
+      </c>
+      <c r="V117" t="n">
+        <v>1</v>
+      </c>
+      <c r="W117" t="n">
+        <v>24.67100721308353</v>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -5421,6 +7650,25 @@
       <c r="T118" t="n">
         <v>1</v>
       </c>
+      <c r="U118" t="n">
+        <v>22.5880210441117</v>
+      </c>
+      <c r="V118" t="n">
+        <v>1</v>
+      </c>
+      <c r="W118" t="n">
+        <v>22.5880210441117</v>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -5481,6 +7729,25 @@
       <c r="T119" t="n">
         <v>1</v>
       </c>
+      <c r="U119" t="n">
+        <v>60.66070032316554</v>
+      </c>
+      <c r="V119" t="n">
+        <v>1</v>
+      </c>
+      <c r="W119" t="n">
+        <v>60.66070032316554</v>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -5540,6 +7807,25 @@
       </c>
       <c r="T120" t="n">
         <v>0</v>
+      </c>
+      <c r="U120" t="n">
+        <v>17.78840711600131</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" t="n">
+        <v>17.78840711600131</v>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -5583,6 +7869,25 @@
       <c r="T121" t="n">
         <v>1</v>
       </c>
+      <c r="U121" t="n">
+        <v>85</v>
+      </c>
+      <c r="V121" t="n">
+        <v>1</v>
+      </c>
+      <c r="W121" t="n">
+        <v>85</v>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -5625,6 +7930,25 @@
       <c r="T122" t="n">
         <v>0</v>
       </c>
+      <c r="U122" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0</v>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
@@ -5667,6 +7991,25 @@
       <c r="T123" t="n">
         <v>0</v>
       </c>
+      <c r="U123" t="n">
+        <v>7.701167696477477</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" t="n">
+        <v>7.701167696477477</v>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -5709,6 +8052,25 @@
       <c r="T124" t="n">
         <v>0</v>
       </c>
+      <c r="U124" t="n">
+        <v>0</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0</v>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -5751,6 +8113,25 @@
       <c r="T125" t="n">
         <v>0</v>
       </c>
+      <c r="U125" t="n">
+        <v>0</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0</v>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -5793,6 +8174,25 @@
       <c r="T126" t="n">
         <v>1</v>
       </c>
+      <c r="U126" t="n">
+        <v>72.83536297834375</v>
+      </c>
+      <c r="V126" t="n">
+        <v>1</v>
+      </c>
+      <c r="W126" t="n">
+        <v>72.83536297834375</v>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
@@ -5835,6 +8235,25 @@
       <c r="T127" t="n">
         <v>1</v>
       </c>
+      <c r="U127" t="n">
+        <v>85</v>
+      </c>
+      <c r="V127" t="n">
+        <v>1</v>
+      </c>
+      <c r="W127" t="n">
+        <v>85</v>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -5877,6 +8296,25 @@
       <c r="T128" t="n">
         <v>0</v>
       </c>
+      <c r="U128" t="n">
+        <v>0</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0</v>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
@@ -5919,6 +8357,25 @@
       <c r="T129" t="n">
         <v>0</v>
       </c>
+      <c r="U129" t="n">
+        <v>2.955267333308224</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0</v>
+      </c>
+      <c r="W129" t="n">
+        <v>2.955267333308224</v>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -5961,6 +8418,25 @@
       <c r="T130" t="n">
         <v>0</v>
       </c>
+      <c r="U130" t="n">
+        <v>12.01651108993916</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0</v>
+      </c>
+      <c r="W130" t="n">
+        <v>12.01651108993916</v>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
@@ -6003,6 +8479,25 @@
       <c r="T131" t="n">
         <v>0</v>
       </c>
+      <c r="U131" t="n">
+        <v>0</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0</v>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
@@ -6045,6 +8540,25 @@
       <c r="T132" t="n">
         <v>0</v>
       </c>
+      <c r="U132" t="n">
+        <v>3.557917116730207</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0</v>
+      </c>
+      <c r="W132" t="n">
+        <v>3.557917116730207</v>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
@@ -6087,6 +8601,25 @@
       <c r="T133" t="n">
         <v>0</v>
       </c>
+      <c r="U133" t="n">
+        <v>0</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0</v>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
@@ -6129,6 +8662,25 @@
       <c r="T134" t="n">
         <v>0</v>
       </c>
+      <c r="U134" t="n">
+        <v>0</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0</v>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
@@ -6171,6 +8723,25 @@
       <c r="T135" t="n">
         <v>0</v>
       </c>
+      <c r="U135" t="n">
+        <v>28.36907184222885</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0</v>
+      </c>
+      <c r="W135" t="n">
+        <v>28.36907184222885</v>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
@@ -6213,6 +8784,25 @@
       <c r="T136" t="n">
         <v>0</v>
       </c>
+      <c r="U136" t="n">
+        <v>0</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
@@ -6255,6 +8845,25 @@
       <c r="T137" t="n">
         <v>0</v>
       </c>
+      <c r="U137" t="n">
+        <v>6.855601653313372</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0</v>
+      </c>
+      <c r="W137" t="n">
+        <v>6.855601653313372</v>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
@@ -6297,6 +8906,25 @@
       <c r="T138" t="n">
         <v>0</v>
       </c>
+      <c r="U138" t="n">
+        <v>7.255770011111526</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0</v>
+      </c>
+      <c r="W138" t="n">
+        <v>7.255770011111526</v>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
@@ -6339,6 +8967,25 @@
       <c r="T139" t="n">
         <v>0</v>
       </c>
+      <c r="U139" t="n">
+        <v>0</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0</v>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
@@ -6381,6 +9028,25 @@
       <c r="T140" t="n">
         <v>0</v>
       </c>
+      <c r="U140" t="n">
+        <v>0</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0</v>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
@@ -6423,6 +9089,25 @@
       <c r="T141" t="n">
         <v>0</v>
       </c>
+      <c r="U141" t="n">
+        <v>0</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0</v>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
@@ -6465,6 +9150,25 @@
       <c r="T142" t="n">
         <v>0</v>
       </c>
+      <c r="U142" t="n">
+        <v>0</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0</v>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
@@ -6507,6 +9211,25 @@
       <c r="T143" t="n">
         <v>0</v>
       </c>
+      <c r="U143" t="n">
+        <v>0.9531203030506304</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.9531203030506304</v>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
@@ -6549,6 +9272,25 @@
       <c r="T144" t="n">
         <v>0</v>
       </c>
+      <c r="U144" t="n">
+        <v>0</v>
+      </c>
+      <c r="V144" t="n">
+        <v>0</v>
+      </c>
+      <c r="W144" t="n">
+        <v>0</v>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
@@ -6591,6 +9333,25 @@
       <c r="T145" t="n">
         <v>1</v>
       </c>
+      <c r="U145" t="n">
+        <v>85</v>
+      </c>
+      <c r="V145" t="n">
+        <v>1</v>
+      </c>
+      <c r="W145" t="n">
+        <v>85</v>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
@@ -6633,6 +9394,25 @@
       <c r="T146" t="n">
         <v>0</v>
       </c>
+      <c r="U146" t="n">
+        <v>0</v>
+      </c>
+      <c r="V146" t="n">
+        <v>0</v>
+      </c>
+      <c r="W146" t="n">
+        <v>0</v>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
@@ -6675,6 +9455,25 @@
       <c r="T147" t="n">
         <v>0</v>
       </c>
+      <c r="U147" t="n">
+        <v>22.59664892478013</v>
+      </c>
+      <c r="V147" t="n">
+        <v>0</v>
+      </c>
+      <c r="W147" t="n">
+        <v>22.59664892478013</v>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
@@ -6717,6 +9516,25 @@
       <c r="T148" t="n">
         <v>0</v>
       </c>
+      <c r="U148" t="n">
+        <v>3.932690435454125</v>
+      </c>
+      <c r="V148" t="n">
+        <v>0</v>
+      </c>
+      <c r="W148" t="n">
+        <v>3.932690435454125</v>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
@@ -6759,6 +9577,25 @@
       <c r="T149" t="n">
         <v>0</v>
       </c>
+      <c r="U149" t="n">
+        <v>0</v>
+      </c>
+      <c r="V149" t="n">
+        <v>0</v>
+      </c>
+      <c r="W149" t="n">
+        <v>0</v>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
@@ -6801,6 +9638,25 @@
       <c r="T150" t="n">
         <v>0</v>
       </c>
+      <c r="U150" t="n">
+        <v>25.58734275782567</v>
+      </c>
+      <c r="V150" t="n">
+        <v>0</v>
+      </c>
+      <c r="W150" t="n">
+        <v>25.58734275782567</v>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
@@ -6843,6 +9699,25 @@
       <c r="T151" t="n">
         <v>0</v>
       </c>
+      <c r="U151" t="n">
+        <v>4.683088100260058</v>
+      </c>
+      <c r="V151" t="n">
+        <v>0</v>
+      </c>
+      <c r="W151" t="n">
+        <v>4.683088100260058</v>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
@@ -6885,6 +9760,25 @@
       <c r="T152" t="n">
         <v>0</v>
       </c>
+      <c r="U152" t="n">
+        <v>0</v>
+      </c>
+      <c r="V152" t="n">
+        <v>0</v>
+      </c>
+      <c r="W152" t="n">
+        <v>0</v>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
@@ -6927,6 +9821,25 @@
       <c r="T153" t="n">
         <v>0</v>
       </c>
+      <c r="U153" t="n">
+        <v>0</v>
+      </c>
+      <c r="V153" t="n">
+        <v>0</v>
+      </c>
+      <c r="W153" t="n">
+        <v>0</v>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
@@ -6969,6 +9882,25 @@
       <c r="T154" t="n">
         <v>0</v>
       </c>
+      <c r="U154" t="n">
+        <v>0</v>
+      </c>
+      <c r="V154" t="n">
+        <v>0</v>
+      </c>
+      <c r="W154" t="n">
+        <v>0</v>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
@@ -7011,6 +9943,25 @@
       <c r="T155" t="n">
         <v>0</v>
       </c>
+      <c r="U155" t="n">
+        <v>41.41312842043301</v>
+      </c>
+      <c r="V155" t="n">
+        <v>0</v>
+      </c>
+      <c r="W155" t="n">
+        <v>41.41312842043301</v>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
@@ -7062,6 +10013,25 @@
       <c r="S156" t="inlineStr"/>
       <c r="T156" t="n">
         <v>0</v>
+      </c>
+      <c r="U156" t="n">
+        <v>24.17281856522927</v>
+      </c>
+      <c r="V156" t="n">
+        <v>0</v>
+      </c>
+      <c r="W156" t="n">
+        <v>24.17281856522927</v>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
       </c>
     </row>
     <row r="157">
@@ -7105,6 +10075,25 @@
       <c r="T157" t="n">
         <v>1</v>
       </c>
+      <c r="U157" t="n">
+        <v>85</v>
+      </c>
+      <c r="V157" t="n">
+        <v>1</v>
+      </c>
+      <c r="W157" t="n">
+        <v>85</v>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
@@ -7147,6 +10136,25 @@
       <c r="T158" t="n">
         <v>0</v>
       </c>
+      <c r="U158" t="n">
+        <v>0</v>
+      </c>
+      <c r="V158" t="n">
+        <v>0</v>
+      </c>
+      <c r="W158" t="n">
+        <v>0</v>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
@@ -7189,6 +10197,25 @@
       <c r="T159" t="n">
         <v>0</v>
       </c>
+      <c r="U159" t="n">
+        <v>0</v>
+      </c>
+      <c r="V159" t="n">
+        <v>0</v>
+      </c>
+      <c r="W159" t="n">
+        <v>0</v>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
@@ -7231,6 +10258,25 @@
       <c r="T160" t="n">
         <v>0</v>
       </c>
+      <c r="U160" t="n">
+        <v>0</v>
+      </c>
+      <c r="V160" t="n">
+        <v>0</v>
+      </c>
+      <c r="W160" t="n">
+        <v>0</v>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
@@ -7273,6 +10319,25 @@
       <c r="T161" t="n">
         <v>0</v>
       </c>
+      <c r="U161" t="n">
+        <v>0</v>
+      </c>
+      <c r="V161" t="n">
+        <v>0</v>
+      </c>
+      <c r="W161" t="n">
+        <v>0</v>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
@@ -7315,6 +10380,25 @@
       <c r="T162" t="n">
         <v>0</v>
       </c>
+      <c r="U162" t="n">
+        <v>12.90465212873485</v>
+      </c>
+      <c r="V162" t="n">
+        <v>0</v>
+      </c>
+      <c r="W162" t="n">
+        <v>12.90465212873485</v>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
@@ -7357,6 +10441,25 @@
       <c r="T163" t="n">
         <v>0</v>
       </c>
+      <c r="U163" t="n">
+        <v>7.761731830233405</v>
+      </c>
+      <c r="V163" t="n">
+        <v>0</v>
+      </c>
+      <c r="W163" t="n">
+        <v>7.761731830233405</v>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
@@ -7399,6 +10502,25 @@
       <c r="T164" t="n">
         <v>0</v>
       </c>
+      <c r="U164" t="n">
+        <v>0</v>
+      </c>
+      <c r="V164" t="n">
+        <v>0</v>
+      </c>
+      <c r="W164" t="n">
+        <v>0</v>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
@@ -7441,6 +10563,25 @@
       <c r="T165" t="n">
         <v>0</v>
       </c>
+      <c r="U165" t="n">
+        <v>12.92567482731039</v>
+      </c>
+      <c r="V165" t="n">
+        <v>0</v>
+      </c>
+      <c r="W165" t="n">
+        <v>12.92567482731039</v>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
@@ -7492,6 +10633,25 @@
       <c r="S166" t="inlineStr"/>
       <c r="T166" t="n">
         <v>0</v>
+      </c>
+      <c r="U166" t="n">
+        <v>2.914456823089139</v>
+      </c>
+      <c r="V166" t="n">
+        <v>0</v>
+      </c>
+      <c r="W166" t="n">
+        <v>2.914456823089139</v>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
       </c>
     </row>
     <row r="167">
@@ -7549,6 +10709,25 @@
       <c r="T167" t="n">
         <v>1</v>
       </c>
+      <c r="U167" t="n">
+        <v>17.20574713356186</v>
+      </c>
+      <c r="V167" t="n">
+        <v>1</v>
+      </c>
+      <c r="W167" t="n">
+        <v>17.20574713356186</v>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
@@ -7605,6 +10784,25 @@
       <c r="T168" t="n">
         <v>1</v>
       </c>
+      <c r="U168" t="n">
+        <v>21.3087762612313</v>
+      </c>
+      <c r="V168" t="n">
+        <v>1</v>
+      </c>
+      <c r="W168" t="n">
+        <v>21.3087762612313</v>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
@@ -7661,6 +10859,25 @@
       <c r="T169" t="n">
         <v>1</v>
       </c>
+      <c r="U169" t="n">
+        <v>31.80692237098406</v>
+      </c>
+      <c r="V169" t="n">
+        <v>1</v>
+      </c>
+      <c r="W169" t="n">
+        <v>31.80692237098406</v>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
@@ -7717,6 +10934,25 @@
       <c r="T170" t="n">
         <v>1</v>
       </c>
+      <c r="U170" t="n">
+        <v>15</v>
+      </c>
+      <c r="V170" t="n">
+        <v>1</v>
+      </c>
+      <c r="W170" t="n">
+        <v>15</v>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
@@ -7773,6 +11009,25 @@
       <c r="T171" t="n">
         <v>1</v>
       </c>
+      <c r="U171" t="n">
+        <v>15</v>
+      </c>
+      <c r="V171" t="n">
+        <v>1</v>
+      </c>
+      <c r="W171" t="n">
+        <v>15</v>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
@@ -7827,6 +11082,25 @@
       <c r="T172" t="n">
         <v>1</v>
       </c>
+      <c r="U172" t="n">
+        <v>17.49749481930035</v>
+      </c>
+      <c r="V172" t="n">
+        <v>1</v>
+      </c>
+      <c r="W172" t="n">
+        <v>17.49749481930035</v>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
@@ -7880,6 +11154,25 @@
       </c>
       <c r="T173" t="n">
         <v>1</v>
+      </c>
+      <c r="U173" t="n">
+        <v>22.44575396567187</v>
+      </c>
+      <c r="V173" t="n">
+        <v>1</v>
+      </c>
+      <c r="W173" t="n">
+        <v>22.44575396567187</v>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
       </c>
     </row>
     <row r="174">
@@ -7918,6 +11211,25 @@
       </c>
       <c r="T174" t="n">
         <v>1</v>
+      </c>
+      <c r="U174" t="n">
+        <v>0</v>
+      </c>
+      <c r="V174" t="n">
+        <v>0</v>
+      </c>
+      <c r="W174" t="n">
+        <v>0</v>
+      </c>
+      <c r="X174" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>ЦБ SORS — основной источник; Росказна — дополнительный индикатор при наличии данных</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -48013,7 +51325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48268,6 +51580,66 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>m5_score</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Итоговый стандартизированный score M5 для LSI, 0–100. Основной вес у данных ЦБ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>m5_flag</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Итоговый флаг M5 для LSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>m5_signal</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Итоговый сигнал M5, равен m5_score</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>source_quality</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Качество источников: high = ЦБ + Росказна, medium = только ЦБ, low = мало данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>m5_comment</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Краткий комментарий по методологии M5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
